--- a/quizzes/002_substance_awareness_quiz--quizzes.xlsx
+++ b/quizzes/002_substance_awareness_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>prevention_programs</t>
+          <t>prevention_programs_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prevention Programs</t>
+          <t>Prevention Programs 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>education_settings</t>
+          <t>education_settings_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Education Settings</t>
+          <t>Education Settings 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assessment_questions</t>
+          <t>assessment_questions_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assessment Questions</t>
+          <t>Assessment Questions 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>prevention_programs_choices</t>
+          <t>prevention_programs_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>prevention_programs_choices</t>
+          <t>prevention_programs_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>education_settings_choices</t>
+          <t>education_settings_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>education_settings_choices</t>
+          <t>education_settings_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
